--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="869">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1290,6 +1290,9 @@
 Occurrence Codes
 Value codes
 </t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>Supporting information</t>
@@ -10443,7 +10446,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>77</v>
@@ -10461,16 +10464,16 @@
         <v>266</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10507,7 +10510,7 @@
         <v>20</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
@@ -10540,10 +10543,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10646,10 +10649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10754,10 +10757,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10864,10 +10867,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10893,14 +10896,14 @@
         <v>378</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10949,7 +10952,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>84</v>
@@ -10972,10 +10975,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11001,16 +11004,16 @@
         <v>159</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11038,10 +11041,10 @@
         <v>254</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -11059,7 +11062,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>84</v>
@@ -11082,10 +11085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11111,14 +11114,14 @@
         <v>159</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11146,10 +11149,10 @@
         <v>254</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11167,7 +11170,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11190,10 +11193,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11296,10 +11299,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11404,10 +11407,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11471,7 +11474,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
@@ -11512,10 +11515,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11622,10 +11625,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11648,13 +11651,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11705,7 +11708,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11728,10 +11731,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11754,19 +11757,19 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11815,7 +11818,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11838,10 +11841,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11867,16 +11870,16 @@
         <v>159</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11904,10 +11907,10 @@
         <v>254</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -11925,7 +11928,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11948,20 +11951,20 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>405</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>406</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>77</v>
@@ -11979,16 +11982,16 @@
         <v>266</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12060,10 +12063,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12166,10 +12169,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12274,10 +12277,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12384,10 +12387,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12413,14 +12416,14 @@
         <v>378</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12469,7 +12472,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>84</v>
@@ -12492,10 +12495,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12521,16 +12524,16 @@
         <v>159</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12540,7 +12543,7 @@
         <v>20</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>20</v>
@@ -12558,10 +12561,10 @@
         <v>254</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12579,7 +12582,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>84</v>
@@ -12602,10 +12605,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12631,14 +12634,14 @@
         <v>159</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12667,7 +12670,7 @@
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -12685,7 +12688,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12703,15 +12706,15 @@
         <v>20</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12814,10 +12817,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12922,10 +12925,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12989,7 +12992,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13030,10 +13033,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13140,10 +13143,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13169,10 +13172,10 @@
         <v>210</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13211,17 +13214,17 @@
         <v>20</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -13244,13 +13247,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>20</v>
@@ -13275,10 +13278,10 @@
         <v>210</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13329,7 +13332,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13347,15 +13350,15 @@
         <v>20</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13378,19 +13381,19 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13439,7 +13442,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13462,10 +13465,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13491,16 +13494,16 @@
         <v>159</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -13528,10 +13531,10 @@
         <v>254</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
@@ -13549,7 +13552,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13572,13 +13575,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>405</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>406</v>
@@ -13603,16 +13606,16 @@
         <v>266</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -13684,10 +13687,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13790,10 +13793,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13898,10 +13901,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14008,10 +14011,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14037,14 +14040,14 @@
         <v>378</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14093,7 +14096,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>84</v>
@@ -14116,10 +14119,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14145,16 +14148,16 @@
         <v>159</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -14164,7 +14167,7 @@
         <v>20</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>20</v>
@@ -14182,10 +14185,10 @@
         <v>254</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>20</v>
@@ -14203,7 +14206,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>84</v>
@@ -14226,10 +14229,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14255,14 +14258,14 @@
         <v>159</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -14290,10 +14293,10 @@
         <v>254</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>20</v>
@@ -14311,7 +14314,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14334,10 +14337,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14440,10 +14443,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14548,10 +14551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14615,7 +14618,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
@@ -14656,10 +14659,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14766,10 +14769,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14792,13 +14795,13 @@
         <v>20</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14849,7 +14852,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14872,10 +14875,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14901,16 +14904,16 @@
         <v>388</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>20</v>
@@ -14959,7 +14962,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14977,15 +14980,15 @@
         <v>20</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15011,16 +15014,16 @@
         <v>159</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -15048,10 +15051,10 @@
         <v>254</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -15069,7 +15072,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -15092,13 +15095,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>405</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>406</v>
@@ -15123,16 +15126,16 @@
         <v>266</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -15204,10 +15207,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15310,10 +15313,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15418,10 +15421,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15528,10 +15531,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15557,14 +15560,14 @@
         <v>378</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -15613,7 +15616,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>84</v>
@@ -15636,10 +15639,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15665,16 +15668,16 @@
         <v>159</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>20</v>
@@ -15684,7 +15687,7 @@
         <v>20</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>20</v>
@@ -15702,10 +15705,10 @@
         <v>254</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>20</v>
@@ -15723,7 +15726,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>84</v>
@@ -15746,10 +15749,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15775,14 +15778,14 @@
         <v>159</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -15810,10 +15813,10 @@
         <v>254</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>20</v>
@@ -15831,7 +15834,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15854,10 +15857,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15960,10 +15963,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16068,10 +16071,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16135,7 +16138,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>20</v>
@@ -16176,10 +16179,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16286,10 +16289,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16312,13 +16315,13 @@
         <v>20</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16369,7 +16372,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16392,10 +16395,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16418,19 +16421,19 @@
         <v>20</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>20</v>
@@ -16467,7 +16470,7 @@
         <v>20</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AC124" s="2"/>
       <c r="AD124" t="s" s="2">
@@ -16477,7 +16480,7 @@
         <v>174</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16500,13 +16503,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>20</v>
@@ -16528,19 +16531,19 @@
         <v>20</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -16589,7 +16592,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16612,10 +16615,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16718,10 +16721,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16826,10 +16829,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16852,19 +16855,19 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>20</v>
@@ -16913,7 +16916,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16931,15 +16934,15 @@
         <v>20</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16965,20 +16968,20 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q129" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="R129" t="s" s="2">
         <v>20</v>
@@ -17002,10 +17005,10 @@
         <v>108</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>20</v>
@@ -17023,7 +17026,7 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -17046,10 +17049,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17075,14 +17078,14 @@
         <v>185</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -17092,7 +17095,7 @@
         <v>20</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>20</v>
@@ -17131,7 +17134,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17154,10 +17157,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17183,14 +17186,14 @@
         <v>98</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>20</v>
@@ -17200,7 +17203,7 @@
         <v>20</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>20</v>
@@ -17239,7 +17242,7 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17248,7 +17251,7 @@
         <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>96</v>
@@ -17262,10 +17265,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17291,16 +17294,16 @@
         <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -17310,7 +17313,7 @@
         <v>20</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>20</v>
@@ -17349,7 +17352,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17358,7 +17361,7 @@
         <v>84</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>96</v>
@@ -17372,10 +17375,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17401,16 +17404,16 @@
         <v>159</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>20</v>
@@ -17438,10 +17441,10 @@
         <v>254</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>20</v>
@@ -17459,7 +17462,7 @@
         <v>20</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17482,10 +17485,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17511,14 +17514,14 @@
         <v>266</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>20</v>
@@ -17567,7 +17570,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17590,10 +17593,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17696,10 +17699,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17804,10 +17807,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17914,10 +17917,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17943,16 +17946,16 @@
         <v>378</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -18001,7 +18004,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>84</v>
@@ -18024,10 +18027,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18050,17 +18053,17 @@
         <v>20</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -18109,7 +18112,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -18132,10 +18135,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18161,16 +18164,16 @@
         <v>159</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -18198,10 +18201,10 @@
         <v>254</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>20</v>
@@ -18219,7 +18222,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18242,10 +18245,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18271,14 +18274,14 @@
         <v>159</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>20</v>
@@ -18306,10 +18309,10 @@
         <v>254</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>20</v>
@@ -18327,7 +18330,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18350,10 +18353,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18379,14 +18382,14 @@
         <v>266</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -18435,7 +18438,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18458,10 +18461,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18564,10 +18567,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18672,10 +18675,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18782,10 +18785,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18811,14 +18814,14 @@
         <v>378</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>20</v>
@@ -18867,7 +18870,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>84</v>
@@ -18890,10 +18893,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18919,16 +18922,16 @@
         <v>159</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>20</v>
@@ -18956,10 +18959,10 @@
         <v>254</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>20</v>
@@ -18977,7 +18980,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19000,10 +19003,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19029,14 +19032,14 @@
         <v>218</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>20</v>
@@ -19085,7 +19088,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19108,10 +19111,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19134,17 +19137,17 @@
         <v>20</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>20</v>
@@ -19172,10 +19175,10 @@
         <v>254</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>20</v>
@@ -19193,7 +19196,7 @@
         <v>20</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>84</v>
@@ -19216,10 +19219,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19242,17 +19245,17 @@
         <v>20</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>20</v>
@@ -19301,7 +19304,7 @@
         <v>20</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -19324,10 +19327,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19353,16 +19356,16 @@
         <v>266</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>20</v>
@@ -19411,7 +19414,7 @@
         <v>20</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19434,10 +19437,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19540,10 +19543,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19648,10 +19651,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19758,10 +19761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19787,14 +19790,14 @@
         <v>378</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>20</v>
@@ -19843,7 +19846,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>84</v>
@@ -19866,10 +19869,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19895,16 +19898,16 @@
         <v>388</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>20</v>
@@ -19953,7 +19956,7 @@
         <v>20</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>84</v>
@@ -19976,10 +19979,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20005,16 +20008,16 @@
         <v>143</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>20</v>
@@ -20063,7 +20066,7 @@
         <v>20</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -20086,10 +20089,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20112,17 +20115,17 @@
         <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>20</v>
@@ -20171,7 +20174,7 @@
         <v>20</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -20194,10 +20197,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20223,14 +20226,14 @@
         <v>185</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>20</v>
@@ -20279,7 +20282,7 @@
         <v>20</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20302,10 +20305,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20331,16 +20334,16 @@
         <v>185</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>20</v>
@@ -20389,7 +20392,7 @@
         <v>20</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20412,10 +20415,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20438,19 +20441,19 @@
         <v>20</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -20499,7 +20502,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20522,10 +20525,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20551,14 +20554,14 @@
         <v>266</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>20</v>
@@ -20607,7 +20610,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20630,10 +20633,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20736,10 +20739,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20844,10 +20847,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20954,10 +20957,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20980,19 +20983,19 @@
         <v>20</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>20</v>
@@ -21041,7 +21044,7 @@
         <v>20</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>84</v>
@@ -21059,15 +21062,15 @@
         <v>20</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21093,14 +21096,14 @@
         <v>159</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>20</v>
@@ -21129,7 +21132,7 @@
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>20</v>
@@ -21147,7 +21150,7 @@
         <v>20</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -21165,15 +21168,15 @@
         <v>20</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21196,17 +21199,17 @@
         <v>20</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>20</v>
@@ -21255,7 +21258,7 @@
         <v>20</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -21278,10 +21281,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21304,17 +21307,17 @@
         <v>20</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>20</v>
@@ -21363,7 +21366,7 @@
         <v>20</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21386,10 +21389,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21415,14 +21418,14 @@
         <v>266</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>20</v>
@@ -21471,7 +21474,7 @@
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -21494,10 +21497,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21600,10 +21603,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21708,10 +21711,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21818,10 +21821,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21847,14 +21850,14 @@
         <v>378</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>20</v>
@@ -21903,7 +21906,7 @@
         <v>20</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>84</v>
@@ -21926,10 +21929,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22011,7 +22014,7 @@
         <v>20</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22034,10 +22037,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22063,14 +22066,14 @@
         <v>378</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>20</v>
@@ -22119,7 +22122,7 @@
         <v>20</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22142,10 +22145,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22171,14 +22174,14 @@
         <v>378</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>20</v>
@@ -22227,7 +22230,7 @@
         <v>20</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -22250,10 +22253,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22279,14 +22282,14 @@
         <v>378</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>20</v>
@@ -22335,7 +22338,7 @@
         <v>20</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -22358,10 +22361,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22387,14 +22390,14 @@
         <v>378</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>20</v>
@@ -22443,7 +22446,7 @@
         <v>20</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22466,10 +22469,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22495,14 +22498,14 @@
         <v>159</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>20</v>
@@ -22530,10 +22533,10 @@
         <v>254</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>20</v>
@@ -22551,7 +22554,7 @@
         <v>20</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22574,10 +22577,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22603,16 +22606,16 @@
         <v>159</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>20</v>
@@ -22640,10 +22643,10 @@
         <v>254</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>20</v>
@@ -22661,7 +22664,7 @@
         <v>20</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22684,14 +22687,14 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -22713,16 +22716,16 @@
         <v>159</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>20</v>
@@ -22750,10 +22753,10 @@
         <v>254</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>20</v>
@@ -22771,7 +22774,7 @@
         <v>20</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -22794,14 +22797,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -22823,10 +22826,10 @@
         <v>159</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22857,7 +22860,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>20</v>
@@ -22875,7 +22878,7 @@
         <v>20</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -22898,10 +22901,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22924,17 +22927,17 @@
         <v>20</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>20</v>
@@ -22983,7 +22986,7 @@
         <v>20</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23006,10 +23009,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23035,16 +23038,16 @@
         <v>159</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>20</v>
@@ -23072,10 +23075,10 @@
         <v>254</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>20</v>
@@ -23093,7 +23096,7 @@
         <v>20</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -23116,10 +23119,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23145,16 +23148,16 @@
         <v>159</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>20</v>
@@ -23182,10 +23185,10 @@
         <v>254</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>20</v>
@@ -23203,7 +23206,7 @@
         <v>20</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>
@@ -23226,10 +23229,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23252,17 +23255,17 @@
         <v>20</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>20</v>
@@ -23311,7 +23314,7 @@
         <v>20</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>76</v>
@@ -23334,10 +23337,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23360,17 +23363,17 @@
         <v>20</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>20</v>
@@ -23398,10 +23401,10 @@
         <v>254</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>20</v>
@@ -23419,7 +23422,7 @@
         <v>20</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>76</v>
@@ -23442,10 +23445,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23468,17 +23471,17 @@
         <v>20</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>20</v>
@@ -23527,7 +23530,7 @@
         <v>20</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>76</v>
@@ -23550,10 +23553,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23576,17 +23579,17 @@
         <v>20</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>20</v>
@@ -23635,7 +23638,7 @@
         <v>20</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -23658,10 +23661,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23684,17 +23687,17 @@
         <v>20</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>20</v>
@@ -23743,7 +23746,7 @@
         <v>20</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>76</v>
@@ -23766,10 +23769,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23792,19 +23795,19 @@
         <v>20</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>20</v>
@@ -23853,7 +23856,7 @@
         <v>20</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>76</v>
@@ -23876,10 +23879,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23902,17 +23905,17 @@
         <v>20</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>20</v>
@@ -23961,7 +23964,7 @@
         <v>20</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>76</v>
@@ -23984,10 +23987,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24010,19 +24013,19 @@
         <v>20</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>20</v>
@@ -24071,7 +24074,7 @@
         <v>20</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>76</v>
@@ -24094,10 +24097,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24120,17 +24123,17 @@
         <v>20</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>20</v>
@@ -24179,7 +24182,7 @@
         <v>20</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>76</v>
@@ -24202,10 +24205,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24231,10 +24234,10 @@
         <v>266</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24285,7 +24288,7 @@
         <v>20</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>76</v>
@@ -24308,10 +24311,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24414,10 +24417,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24522,10 +24525,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24632,10 +24635,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24658,19 +24661,19 @@
         <v>20</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>20</v>
@@ -24699,7 +24702,7 @@
       </c>
       <c r="Y200" s="2"/>
       <c r="Z200" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>20</v>
@@ -24717,7 +24720,7 @@
         <v>20</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>84</v>
@@ -24740,10 +24743,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24769,14 +24772,14 @@
         <v>159</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>20</v>
@@ -24805,7 +24808,7 @@
       </c>
       <c r="Y201" s="2"/>
       <c r="Z201" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>20</v>
@@ -24823,7 +24826,7 @@
         <v>20</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>76</v>
@@ -24846,10 +24849,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24933,7 +24936,7 @@
         <v>20</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>76</v>
@@ -24956,10 +24959,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24985,14 +24988,14 @@
         <v>266</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>20</v>
@@ -25041,7 +25044,7 @@
         <v>20</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>76</v>
@@ -25064,10 +25067,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25170,10 +25173,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25278,10 +25281,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25388,10 +25391,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25417,14 +25420,14 @@
         <v>378</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>20</v>
@@ -25473,7 +25476,7 @@
         <v>20</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>84</v>
@@ -25496,10 +25499,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25581,7 +25584,7 @@
         <v>20</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>76</v>
@@ -25604,10 +25607,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25633,14 +25636,14 @@
         <v>159</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25668,10 +25671,10 @@
         <v>254</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>20</v>
@@ -25689,7 +25692,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>76</v>
@@ -25712,10 +25715,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25741,16 +25744,16 @@
         <v>159</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>20</v>
@@ -25778,10 +25781,10 @@
         <v>254</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>20</v>
@@ -25799,7 +25802,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>76</v>
@@ -25822,14 +25825,14 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
@@ -25851,16 +25854,16 @@
         <v>159</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>20</v>
@@ -25888,10 +25891,10 @@
         <v>254</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>20</v>
@@ -25909,7 +25912,7 @@
         <v>20</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>76</v>
@@ -25932,14 +25935,14 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -25961,10 +25964,10 @@
         <v>159</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -25995,7 +25998,7 @@
       </c>
       <c r="Y212" s="2"/>
       <c r="Z212" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>20</v>
@@ -26013,7 +26016,7 @@
         <v>20</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>76</v>
@@ -26036,10 +26039,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26065,16 +26068,16 @@
         <v>159</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>20</v>
@@ -26102,10 +26105,10 @@
         <v>254</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>20</v>
@@ -26123,7 +26126,7 @@
         <v>20</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>76</v>
@@ -26146,10 +26149,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26175,16 +26178,16 @@
         <v>159</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>20</v>
@@ -26212,10 +26215,10 @@
         <v>254</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>20</v>
@@ -26233,7 +26236,7 @@
         <v>20</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>76</v>
@@ -26256,10 +26259,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26282,17 +26285,17 @@
         <v>20</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>20</v>
@@ -26341,7 +26344,7 @@
         <v>20</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -26364,10 +26367,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26390,17 +26393,17 @@
         <v>20</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>20</v>
@@ -26449,7 +26452,7 @@
         <v>20</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>76</v>
@@ -26472,10 +26475,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26498,17 +26501,17 @@
         <v>20</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>20</v>
@@ -26557,7 +26560,7 @@
         <v>20</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>76</v>
@@ -26580,10 +26583,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26606,19 +26609,19 @@
         <v>20</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>20</v>
@@ -26667,7 +26670,7 @@
         <v>20</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>76</v>
@@ -26690,10 +26693,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26716,17 +26719,17 @@
         <v>20</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>20</v>
@@ -26775,7 +26778,7 @@
         <v>20</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>76</v>
@@ -26798,10 +26801,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26824,19 +26827,19 @@
         <v>20</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>20</v>
@@ -26885,7 +26888,7 @@
         <v>20</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>76</v>
@@ -26908,10 +26911,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26934,17 +26937,17 @@
         <v>20</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>20</v>
@@ -26993,7 +26996,7 @@
         <v>20</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>76</v>
@@ -27016,10 +27019,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -27045,14 +27048,14 @@
         <v>266</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>20</v>
@@ -27101,7 +27104,7 @@
         <v>20</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>76</v>
@@ -27124,10 +27127,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -27230,10 +27233,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27338,10 +27341,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -27448,10 +27451,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -27477,14 +27480,14 @@
         <v>378</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>20</v>
@@ -27533,7 +27536,7 @@
         <v>20</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>84</v>
@@ -27556,10 +27559,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27641,7 +27644,7 @@
         <v>20</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>76</v>
@@ -27664,10 +27667,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27693,14 +27696,14 @@
         <v>159</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>20</v>
@@ -27728,10 +27731,10 @@
         <v>254</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>20</v>
@@ -27749,7 +27752,7 @@
         <v>20</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>76</v>
@@ -27772,10 +27775,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27801,16 +27804,16 @@
         <v>159</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>20</v>
@@ -27838,10 +27841,10 @@
         <v>254</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>20</v>
@@ -27859,7 +27862,7 @@
         <v>20</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>76</v>
@@ -27882,10 +27885,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27911,16 +27914,16 @@
         <v>159</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>20</v>
@@ -27948,10 +27951,10 @@
         <v>254</v>
       </c>
       <c r="Y230" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="Z230" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>20</v>
@@ -27969,7 +27972,7 @@
         <v>20</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>76</v>
@@ -27992,14 +27995,14 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
@@ -28021,10 +28024,10 @@
         <v>159</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -28055,7 +28058,7 @@
       </c>
       <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>20</v>
@@ -28073,7 +28076,7 @@
         <v>20</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>76</v>
@@ -28096,10 +28099,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -28125,16 +28128,16 @@
         <v>159</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>20</v>
@@ -28162,10 +28165,10 @@
         <v>254</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>20</v>
@@ -28183,7 +28186,7 @@
         <v>20</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>76</v>
@@ -28206,10 +28209,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28235,16 +28238,16 @@
         <v>159</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>20</v>
@@ -28272,10 +28275,10 @@
         <v>254</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>20</v>
@@ -28293,7 +28296,7 @@
         <v>20</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>76</v>
@@ -28316,10 +28319,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28342,17 +28345,17 @@
         <v>20</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>20</v>
@@ -28401,7 +28404,7 @@
         <v>20</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>76</v>
@@ -28424,10 +28427,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28450,17 +28453,17 @@
         <v>20</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>20</v>
@@ -28509,7 +28512,7 @@
         <v>20</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>76</v>
@@ -28532,10 +28535,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28558,17 +28561,17 @@
         <v>20</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>20</v>
@@ -28617,7 +28620,7 @@
         <v>20</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>76</v>
@@ -28640,10 +28643,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28666,19 +28669,19 @@
         <v>20</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>20</v>
@@ -28727,7 +28730,7 @@
         <v>20</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>76</v>
@@ -28750,10 +28753,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28776,17 +28779,17 @@
         <v>20</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>20</v>
@@ -28835,7 +28838,7 @@
         <v>20</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>76</v>
@@ -28858,10 +28861,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -28884,19 +28887,19 @@
         <v>20</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="O239" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>20</v>
@@ -28945,7 +28948,7 @@
         <v>20</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>76</v>
@@ -28968,10 +28971,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -28994,17 +28997,17 @@
         <v>20</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>20</v>
@@ -29053,7 +29056,7 @@
         <v>20</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>76</v>
@@ -29076,10 +29079,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -29102,17 +29105,17 @@
         <v>20</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>20</v>
@@ -29161,7 +29164,7 @@
         <v>20</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>76</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="870">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1771,6 +1771,9 @@
   </si>
   <si>
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -17313,7 +17316,7 @@
         <v>20</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>20</v>
@@ -17352,7 +17355,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17375,7 +17378,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>448</v>
@@ -17485,10 +17488,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17514,14 +17517,14 @@
         <v>266</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>20</v>
@@ -17570,7 +17573,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17593,10 +17596,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17699,10 +17702,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17807,10 +17810,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17917,10 +17920,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17946,16 +17949,16 @@
         <v>378</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -18004,7 +18007,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>84</v>
@@ -18027,10 +18030,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18053,17 +18056,17 @@
         <v>20</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -18112,7 +18115,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -18135,10 +18138,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18164,16 +18167,16 @@
         <v>159</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -18201,10 +18204,10 @@
         <v>254</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>20</v>
@@ -18222,7 +18225,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18245,10 +18248,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18274,14 +18277,14 @@
         <v>159</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>20</v>
@@ -18309,10 +18312,10 @@
         <v>254</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>20</v>
@@ -18330,7 +18333,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18353,10 +18356,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18382,14 +18385,14 @@
         <v>266</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -18438,7 +18441,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18461,10 +18464,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18567,10 +18570,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18675,10 +18678,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18785,10 +18788,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18814,14 +18817,14 @@
         <v>378</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>20</v>
@@ -18870,7 +18873,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>84</v>
@@ -18893,10 +18896,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18922,16 +18925,16 @@
         <v>159</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>20</v>
@@ -18959,10 +18962,10 @@
         <v>254</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>20</v>
@@ -18980,7 +18983,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19003,10 +19006,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19032,14 +19035,14 @@
         <v>218</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>20</v>
@@ -19088,7 +19091,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19111,10 +19114,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19137,17 +19140,17 @@
         <v>20</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>20</v>
@@ -19175,10 +19178,10 @@
         <v>254</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>20</v>
@@ -19196,7 +19199,7 @@
         <v>20</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>84</v>
@@ -19219,10 +19222,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19245,17 +19248,17 @@
         <v>20</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>20</v>
@@ -19304,7 +19307,7 @@
         <v>20</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -19327,10 +19330,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19356,16 +19359,16 @@
         <v>266</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>20</v>
@@ -19414,7 +19417,7 @@
         <v>20</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19437,10 +19440,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19543,10 +19546,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19651,10 +19654,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19761,10 +19764,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19790,14 +19793,14 @@
         <v>378</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>20</v>
@@ -19846,7 +19849,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>84</v>
@@ -19869,10 +19872,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19898,16 +19901,16 @@
         <v>388</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>20</v>
@@ -19956,7 +19959,7 @@
         <v>20</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>84</v>
@@ -19979,10 +19982,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20008,16 +20011,16 @@
         <v>143</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>20</v>
@@ -20066,7 +20069,7 @@
         <v>20</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -20089,10 +20092,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20115,17 +20118,17 @@
         <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>20</v>
@@ -20174,7 +20177,7 @@
         <v>20</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -20197,10 +20200,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20226,14 +20229,14 @@
         <v>185</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>20</v>
@@ -20282,7 +20285,7 @@
         <v>20</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20305,10 +20308,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20334,16 +20337,16 @@
         <v>185</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>20</v>
@@ -20392,7 +20395,7 @@
         <v>20</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20415,10 +20418,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20441,19 +20444,19 @@
         <v>20</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -20502,7 +20505,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20525,10 +20528,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20554,14 +20557,14 @@
         <v>266</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>20</v>
@@ -20610,7 +20613,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20633,10 +20636,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20739,10 +20742,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20847,10 +20850,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20957,10 +20960,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20983,19 +20986,19 @@
         <v>20</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>20</v>
@@ -21044,7 +21047,7 @@
         <v>20</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>84</v>
@@ -21062,15 +21065,15 @@
         <v>20</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21096,14 +21099,14 @@
         <v>159</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>20</v>
@@ -21132,7 +21135,7 @@
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>20</v>
@@ -21150,7 +21153,7 @@
         <v>20</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -21168,15 +21171,15 @@
         <v>20</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21199,17 +21202,17 @@
         <v>20</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>20</v>
@@ -21258,7 +21261,7 @@
         <v>20</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -21281,10 +21284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21307,17 +21310,17 @@
         <v>20</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>20</v>
@@ -21366,7 +21369,7 @@
         <v>20</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21389,10 +21392,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21418,14 +21421,14 @@
         <v>266</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>20</v>
@@ -21474,7 +21477,7 @@
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -21497,10 +21500,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21603,10 +21606,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21711,10 +21714,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21821,10 +21824,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21850,14 +21853,14 @@
         <v>378</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>20</v>
@@ -21906,7 +21909,7 @@
         <v>20</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>84</v>
@@ -21929,10 +21932,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22014,7 +22017,7 @@
         <v>20</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22037,10 +22040,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22066,14 +22069,14 @@
         <v>378</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>20</v>
@@ -22122,7 +22125,7 @@
         <v>20</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22145,10 +22148,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22174,14 +22177,14 @@
         <v>378</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>20</v>
@@ -22230,7 +22233,7 @@
         <v>20</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -22253,10 +22256,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22282,14 +22285,14 @@
         <v>378</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>20</v>
@@ -22338,7 +22341,7 @@
         <v>20</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -22361,10 +22364,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22390,14 +22393,14 @@
         <v>378</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>20</v>
@@ -22446,7 +22449,7 @@
         <v>20</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22469,10 +22472,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22498,14 +22501,14 @@
         <v>159</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>20</v>
@@ -22533,10 +22536,10 @@
         <v>254</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>20</v>
@@ -22554,7 +22557,7 @@
         <v>20</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22577,10 +22580,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22606,16 +22609,16 @@
         <v>159</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>20</v>
@@ -22643,10 +22646,10 @@
         <v>254</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>20</v>
@@ -22664,7 +22667,7 @@
         <v>20</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22687,14 +22690,14 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -22716,16 +22719,16 @@
         <v>159</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>20</v>
@@ -22753,10 +22756,10 @@
         <v>254</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>20</v>
@@ -22774,7 +22777,7 @@
         <v>20</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -22797,14 +22800,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -22826,10 +22829,10 @@
         <v>159</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22860,7 +22863,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>20</v>
@@ -22878,7 +22881,7 @@
         <v>20</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -22901,10 +22904,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22927,17 +22930,17 @@
         <v>20</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>20</v>
@@ -22986,7 +22989,7 @@
         <v>20</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23009,10 +23012,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23038,16 +23041,16 @@
         <v>159</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>20</v>
@@ -23075,10 +23078,10 @@
         <v>254</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>20</v>
@@ -23096,7 +23099,7 @@
         <v>20</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -23119,10 +23122,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23148,16 +23151,16 @@
         <v>159</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>20</v>
@@ -23185,10 +23188,10 @@
         <v>254</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>20</v>
@@ -23206,7 +23209,7 @@
         <v>20</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>
@@ -23229,10 +23232,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23258,14 +23261,14 @@
         <v>439</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>20</v>
@@ -23314,7 +23317,7 @@
         <v>20</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>76</v>
@@ -23337,10 +23340,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23363,17 +23366,17 @@
         <v>20</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>20</v>
@@ -23401,10 +23404,10 @@
         <v>254</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>20</v>
@@ -23422,7 +23425,7 @@
         <v>20</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>76</v>
@@ -23445,10 +23448,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23471,17 +23474,17 @@
         <v>20</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>20</v>
@@ -23530,7 +23533,7 @@
         <v>20</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>76</v>
@@ -23553,10 +23556,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23579,17 +23582,17 @@
         <v>20</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>20</v>
@@ -23638,7 +23641,7 @@
         <v>20</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -23661,10 +23664,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23687,17 +23690,17 @@
         <v>20</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>20</v>
@@ -23746,7 +23749,7 @@
         <v>20</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>76</v>
@@ -23769,10 +23772,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23798,16 +23801,16 @@
         <v>523</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>20</v>
@@ -23856,7 +23859,7 @@
         <v>20</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>76</v>
@@ -23879,10 +23882,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23905,17 +23908,17 @@
         <v>20</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>20</v>
@@ -23964,7 +23967,7 @@
         <v>20</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>76</v>
@@ -23987,10 +23990,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24013,19 +24016,19 @@
         <v>20</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>20</v>
@@ -24074,7 +24077,7 @@
         <v>20</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>76</v>
@@ -24097,10 +24100,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24123,17 +24126,17 @@
         <v>20</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>20</v>
@@ -24182,7 +24185,7 @@
         <v>20</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>76</v>
@@ -24205,10 +24208,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24234,10 +24237,10 @@
         <v>266</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24288,7 +24291,7 @@
         <v>20</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>76</v>
@@ -24311,10 +24314,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24417,10 +24420,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24525,10 +24528,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24635,10 +24638,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24661,19 +24664,19 @@
         <v>20</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>20</v>
@@ -24702,7 +24705,7 @@
       </c>
       <c r="Y200" s="2"/>
       <c r="Z200" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>20</v>
@@ -24720,7 +24723,7 @@
         <v>20</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>84</v>
@@ -24743,10 +24746,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24772,14 +24775,14 @@
         <v>159</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>20</v>
@@ -24808,7 +24811,7 @@
       </c>
       <c r="Y201" s="2"/>
       <c r="Z201" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>20</v>
@@ -24826,7 +24829,7 @@
         <v>20</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>76</v>
@@ -24849,10 +24852,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24936,7 +24939,7 @@
         <v>20</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>76</v>
@@ -24959,10 +24962,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24988,14 +24991,14 @@
         <v>266</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>20</v>
@@ -25044,7 +25047,7 @@
         <v>20</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>76</v>
@@ -25067,10 +25070,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25173,10 +25176,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25281,10 +25284,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25391,10 +25394,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25420,14 +25423,14 @@
         <v>378</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>20</v>
@@ -25476,7 +25479,7 @@
         <v>20</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>84</v>
@@ -25499,10 +25502,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25584,7 +25587,7 @@
         <v>20</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>76</v>
@@ -25607,10 +25610,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25636,14 +25639,14 @@
         <v>159</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25671,10 +25674,10 @@
         <v>254</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>20</v>
@@ -25692,7 +25695,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>76</v>
@@ -25715,10 +25718,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25744,16 +25747,16 @@
         <v>159</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>20</v>
@@ -25781,10 +25784,10 @@
         <v>254</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>20</v>
@@ -25802,7 +25805,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>76</v>
@@ -25825,14 +25828,14 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
@@ -25854,16 +25857,16 @@
         <v>159</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>20</v>
@@ -25891,10 +25894,10 @@
         <v>254</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>20</v>
@@ -25912,7 +25915,7 @@
         <v>20</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>76</v>
@@ -25935,14 +25938,14 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -25964,10 +25967,10 @@
         <v>159</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -25998,7 +26001,7 @@
       </c>
       <c r="Y212" s="2"/>
       <c r="Z212" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>20</v>
@@ -26016,7 +26019,7 @@
         <v>20</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>76</v>
@@ -26039,10 +26042,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26068,16 +26071,16 @@
         <v>159</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>20</v>
@@ -26105,10 +26108,10 @@
         <v>254</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>20</v>
@@ -26126,7 +26129,7 @@
         <v>20</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>76</v>
@@ -26149,10 +26152,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26178,16 +26181,16 @@
         <v>159</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>20</v>
@@ -26215,10 +26218,10 @@
         <v>254</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>20</v>
@@ -26236,7 +26239,7 @@
         <v>20</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>76</v>
@@ -26259,10 +26262,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26285,17 +26288,17 @@
         <v>20</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>20</v>
@@ -26344,7 +26347,7 @@
         <v>20</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -26367,10 +26370,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26393,17 +26396,17 @@
         <v>20</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>20</v>
@@ -26452,7 +26455,7 @@
         <v>20</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>76</v>
@@ -26475,10 +26478,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26501,17 +26504,17 @@
         <v>20</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>20</v>
@@ -26560,7 +26563,7 @@
         <v>20</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>76</v>
@@ -26583,10 +26586,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26612,16 +26615,16 @@
         <v>523</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>20</v>
@@ -26670,7 +26673,7 @@
         <v>20</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>76</v>
@@ -26693,10 +26696,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26719,17 +26722,17 @@
         <v>20</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>20</v>
@@ -26778,7 +26781,7 @@
         <v>20</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>76</v>
@@ -26801,10 +26804,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26827,19 +26830,19 @@
         <v>20</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>20</v>
@@ -26888,7 +26891,7 @@
         <v>20</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>76</v>
@@ -26911,10 +26914,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26937,17 +26940,17 @@
         <v>20</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>20</v>
@@ -26996,7 +26999,7 @@
         <v>20</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>76</v>
@@ -27019,10 +27022,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -27048,14 +27051,14 @@
         <v>266</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>20</v>
@@ -27104,7 +27107,7 @@
         <v>20</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>76</v>
@@ -27127,10 +27130,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -27233,10 +27236,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27341,10 +27344,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -27451,10 +27454,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -27480,14 +27483,14 @@
         <v>378</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>20</v>
@@ -27536,7 +27539,7 @@
         <v>20</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>84</v>
@@ -27559,10 +27562,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27644,7 +27647,7 @@
         <v>20</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>76</v>
@@ -27667,10 +27670,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27696,14 +27699,14 @@
         <v>159</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>20</v>
@@ -27731,10 +27734,10 @@
         <v>254</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>20</v>
@@ -27752,7 +27755,7 @@
         <v>20</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>76</v>
@@ -27775,10 +27778,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27804,16 +27807,16 @@
         <v>159</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>20</v>
@@ -27841,10 +27844,10 @@
         <v>254</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>20</v>
@@ -27862,7 +27865,7 @@
         <v>20</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>76</v>
@@ -27885,10 +27888,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27914,16 +27917,16 @@
         <v>159</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>20</v>
@@ -27951,10 +27954,10 @@
         <v>254</v>
       </c>
       <c r="Y230" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="Z230" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>20</v>
@@ -27972,7 +27975,7 @@
         <v>20</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>76</v>
@@ -27995,14 +27998,14 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
@@ -28024,10 +28027,10 @@
         <v>159</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -28058,7 +28061,7 @@
       </c>
       <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>20</v>
@@ -28076,7 +28079,7 @@
         <v>20</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>76</v>
@@ -28099,10 +28102,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -28128,16 +28131,16 @@
         <v>159</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>20</v>
@@ -28165,10 +28168,10 @@
         <v>254</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>20</v>
@@ -28186,7 +28189,7 @@
         <v>20</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>76</v>
@@ -28209,10 +28212,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28238,16 +28241,16 @@
         <v>159</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>20</v>
@@ -28275,10 +28278,10 @@
         <v>254</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>20</v>
@@ -28296,7 +28299,7 @@
         <v>20</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>76</v>
@@ -28319,10 +28322,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28345,17 +28348,17 @@
         <v>20</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>20</v>
@@ -28404,7 +28407,7 @@
         <v>20</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>76</v>
@@ -28427,10 +28430,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28453,17 +28456,17 @@
         <v>20</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>20</v>
@@ -28512,7 +28515,7 @@
         <v>20</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>76</v>
@@ -28535,10 +28538,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28561,17 +28564,17 @@
         <v>20</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>20</v>
@@ -28620,7 +28623,7 @@
         <v>20</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>76</v>
@@ -28643,10 +28646,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28672,16 +28675,16 @@
         <v>523</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>20</v>
@@ -28730,7 +28733,7 @@
         <v>20</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>76</v>
@@ -28753,10 +28756,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28779,17 +28782,17 @@
         <v>20</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>20</v>
@@ -28838,7 +28841,7 @@
         <v>20</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>76</v>
@@ -28861,10 +28864,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -28887,19 +28890,19 @@
         <v>20</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="O239" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>20</v>
@@ -28948,7 +28951,7 @@
         <v>20</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>76</v>
@@ -28971,10 +28974,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -28997,17 +29000,17 @@
         <v>20</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>20</v>
@@ -29056,7 +29059,7 @@
         <v>20</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>76</v>
@@ -29079,10 +29082,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -29105,17 +29108,17 @@
         <v>20</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>20</v>
@@ -29164,7 +29167,7 @@
         <v>20</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>76</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -784,7 +784,7 @@
     <t>Claim.provider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KHOrganization)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KAOrganization)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,7 +658,7 @@
     <t>Claim.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedPatient)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK|https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname)
 </t>
   </si>
   <si>
@@ -3029,7 +3029,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="116.35546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="118.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
